--- a/docs/sample-output/04-warehouse/proforma.xlsx
+++ b/docs/sample-output/04-warehouse/proforma.xlsx
@@ -264,7 +264,7 @@
     <t>Leverage Impact</t>
   </si>
   <si>
-    <t>Optimal holding period: Year 5 at -10.53% equity IRR. Leverage is positive when the equity IRR exceeds the property IRR.</t>
+    <t>Optimal holding period: Year 5 at -10.11% equity IRR. Leverage is positive when the equity IRR exceeds the property IRR.</t>
   </si>
   <si>
     <t>Acquisition-Price Sensitivity   ·   I-20 Logistics Center — bulk warehouse · 5-Year Before-Tax</t>
@@ -1073,7 +1073,7 @@
         <v>18</v>
       </c>
       <c r="B13" s="6">
-        <v>47315978.11</v>
+        <v>47072339.2</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -1081,7 +1081,7 @@
         <v>19</v>
       </c>
       <c r="B14" s="7">
-        <v>0.04285402270002868</v>
+        <v>0.04307582827751207</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1089,7 +1089,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="6">
-        <v>16868146.196215004</v>
+        <v>16781288.9248</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -1105,7 +1105,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="7">
-        <v>-0.1053452771446969</v>
+        <v>-0.10107118499026635</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -1113,7 +1113,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="8">
-        <v>0.5507233359706867</v>
+        <v>0.5659433222808465</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -1129,7 +1129,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="7">
-        <v>-0.1053452771446969</v>
+        <v>-0.10107118499026635</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -1144,7 +1144,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="6">
-        <v>47315978.11</v>
+        <v>47072339.2</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -1160,7 +1160,7 @@
         <v>29</v>
       </c>
       <c r="B24" s="6">
-        <v>307553.857715</v>
+        <v>305970.20480000007</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -1168,7 +1168,7 @@
         <v>30</v>
       </c>
       <c r="B25" s="6">
-        <v>47315978.11</v>
+        <v>47072339.2</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -1176,7 +1176,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="6">
-        <v>-30755385.7715</v>
+        <v>-30597020.480000004</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -1184,7 +1184,7 @@
         <v>32</v>
       </c>
       <c r="B27" s="10">
-        <v>16868146.196215004</v>
+        <v>16781288.9248</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -1192,7 +1192,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="11">
-        <v>20.39481815086207</v>
+        <v>20.289801379310347</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -1200,7 +1200,7 @@
         <v>34</v>
       </c>
       <c r="B29" s="12">
-        <v>147.86243159375</v>
+        <v>147.10106000000002</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -1215,7 +1215,7 @@
         <v>36</v>
       </c>
       <c r="B31" s="6">
-        <v>30755385.7715</v>
+        <v>30597020.480000004</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -1247,7 +1247,7 @@
         <v>42</v>
       </c>
       <c r="B35" s="12">
-        <v>207662.56722926165</v>
+        <v>206593.2734399646</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -1255,7 +1255,7 @@
         <v>43</v>
       </c>
       <c r="B36" s="6">
-        <v>2491950.80675114</v>
+        <v>2479119.281279575</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -1490,19 +1490,19 @@
         <v>60</v>
       </c>
       <c r="B13" s="16">
-        <v>-2491950.80675114</v>
+        <v>-2479119.281279575</v>
       </c>
       <c r="C13" s="16">
-        <v>-2491950.80675114</v>
+        <v>-2479119.281279575</v>
       </c>
       <c r="D13" s="16">
-        <v>-2491950.80675114</v>
+        <v>-2479119.281279575</v>
       </c>
       <c r="E13" s="16">
-        <v>-2491950.80675114</v>
+        <v>-2479119.281279575</v>
       </c>
       <c r="F13" s="16">
-        <v>-2491950.80675114</v>
+        <v>-2479119.281279575</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1510,19 +1510,19 @@
         <v>61</v>
       </c>
       <c r="B14" s="18">
-        <v>-464270.8067511399</v>
+        <v>-451439.2812795751</v>
       </c>
       <c r="C14" s="18">
-        <v>-403440.40675114</v>
+        <v>-390608.8812795752</v>
       </c>
       <c r="D14" s="18">
-        <v>-340785.09475113964</v>
+        <v>-327953.5692795748</v>
       </c>
       <c r="E14" s="18">
-        <v>-276250.1233911398</v>
+        <v>-263418.59791957494</v>
       </c>
       <c r="F14" s="18">
-        <v>-209779.10289033968</v>
+        <v>-196947.57741877483</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1666,19 +1666,19 @@
         <v>68</v>
       </c>
       <c r="B9" s="16">
-        <v>-30247583.82909532</v>
+        <v>-30091833.305728316</v>
       </c>
       <c r="C9" s="16">
-        <v>-29705773.45015731</v>
+        <v>-29552812.810787726</v>
       </c>
       <c r="D9" s="16">
-        <v>-29127677.026707623</v>
+        <v>-28977693.11503363</v>
       </c>
       <c r="E9" s="16">
-        <v>-28510864.41514346</v>
+        <v>-28364056.588131744</v>
       </c>
       <c r="F9" s="16">
-        <v>-27852742.720644325</v>
+        <v>-27709323.686566837</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1686,19 +1686,19 @@
         <v>69</v>
       </c>
       <c r="B10" s="18">
-        <v>4258316.170904681</v>
+        <v>4414066.694271684</v>
       </c>
       <c r="C10" s="18">
-        <v>5835626.549842689</v>
+        <v>5988587.189212274</v>
       </c>
       <c r="D10" s="18">
-        <v>7479622.973292377</v>
+        <v>7629606.88496637</v>
       </c>
       <c r="E10" s="18">
-        <v>9194635.58485654</v>
+        <v>9341443.411868256</v>
       </c>
       <c r="F10" s="18">
-        <v>10984207.279355675</v>
+        <v>11127626.313433163</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1736,19 +1736,19 @@
         <v>71</v>
       </c>
       <c r="B13" s="21">
-        <v>0.8327620678678299</v>
+        <v>0.8284740186588931</v>
       </c>
       <c r="C13" s="21">
-        <v>0.7940172524900383</v>
+        <v>0.7899287076549697</v>
       </c>
       <c r="D13" s="21">
-        <v>0.7558954955807241</v>
+        <v>0.7520032468737642</v>
       </c>
       <c r="E13" s="21">
-        <v>0.7183387355793263</v>
+        <v>0.7146398737246598</v>
       </c>
       <c r="F13" s="21">
-        <v>0.6813126567511637</v>
+        <v>0.6778044491711758</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1756,19 +1756,19 @@
         <v>72</v>
       </c>
       <c r="B14" s="22">
-        <v>0.8136918250980929</v>
+        <v>0.8179033640339529</v>
       </c>
       <c r="C14" s="22">
-        <v>0.8381025798510356</v>
+        <v>0.8424404649549715</v>
       </c>
       <c r="D14" s="22">
-        <v>0.8632456572465669</v>
+        <v>0.8677136789036207</v>
       </c>
       <c r="E14" s="22">
-        <v>0.8891430269639637</v>
+        <v>0.8937450892707293</v>
       </c>
       <c r="F14" s="22">
-        <v>0.9158173177728828</v>
+        <v>0.9205574419488513</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1776,19 +1776,19 @@
         <v>73</v>
       </c>
       <c r="B15" s="21">
-        <v>0.06592926569235182</v>
+        <v>0.06627050504232626</v>
       </c>
       <c r="C15" s="21">
-        <v>0.06790714366312237</v>
+        <v>0.06825862019359603</v>
       </c>
       <c r="D15" s="21">
-        <v>0.06994435797301606</v>
+        <v>0.07030637879940393</v>
       </c>
       <c r="E15" s="21">
-        <v>0.07204268871220652</v>
+        <v>0.07241557016338605</v>
       </c>
       <c r="F15" s="21">
-        <v>0.07420396937357272</v>
+        <v>0.07458803726828764</v>
       </c>
     </row>
   </sheetData>
@@ -1864,19 +1864,19 @@
         <v>75</v>
       </c>
       <c r="B5" s="21">
-        <v>-0.027523522819319433</v>
+        <v>-0.026901347286406686</v>
       </c>
       <c r="C5" s="21">
-        <v>-0.023917293700102437</v>
+        <v>-0.02327645290120231</v>
       </c>
       <c r="D5" s="21">
-        <v>-0.020202877707308907</v>
+        <v>-0.019542811684441774</v>
       </c>
       <c r="E5" s="21">
-        <v>-0.016377029234731603</v>
+        <v>-0.015697161231178453</v>
       </c>
       <c r="F5" s="21">
-        <v>-0.012436405307976963</v>
+        <v>-0.01173614126431722</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1884,19 +1884,19 @@
         <v>76</v>
       </c>
       <c r="B6" s="21">
-        <v>-0.10902685195695683</v>
+        <v>-0.10227287273783753</v>
       </c>
       <c r="C6" s="21">
-        <v>-0.06913403441863762</v>
+        <v>-0.06522554801960811</v>
       </c>
       <c r="D6" s="21">
-        <v>-0.04556180117206269</v>
+        <v>-0.04298433382272753</v>
       </c>
       <c r="E6" s="21">
-        <v>-0.030044706050789072</v>
+        <v>-0.028198918122749956</v>
       </c>
       <c r="F6" s="21">
-        <v>-0.019098246924437606</v>
+        <v>-0.017698974774253664</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1904,19 +1904,19 @@
         <v>77</v>
       </c>
       <c r="B7" s="23">
-        <v>0.2249236709250763</v>
+        <v>0.23613367428147866</v>
       </c>
       <c r="C7" s="23">
-        <v>0.2945146003924928</v>
+        <v>0.3066831784921706</v>
       </c>
       <c r="D7" s="23">
-        <v>0.37177331712041467</v>
+        <v>0.3849290231563443</v>
       </c>
       <c r="E7" s="23">
-        <v>0.4570679589522399</v>
+        <v>0.4712405058721795</v>
       </c>
       <c r="F7" s="23">
-        <v>0.5507233359706867</v>
+        <v>0.5659433222808465</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1924,19 +1924,19 @@
         <v>78</v>
       </c>
       <c r="B8" s="21">
-        <v>-0.22788069782527948</v>
+        <v>-0.22388433162847696</v>
       </c>
       <c r="C8" s="21">
-        <v>-0.08652544255067492</v>
+        <v>-0.08410763602235116</v>
       </c>
       <c r="D8" s="21">
-        <v>-0.03387247595562593</v>
+        <v>-0.032129301650089655</v>
       </c>
       <c r="E8" s="21">
-        <v>-0.0064392809441367604</v>
+        <v>-0.005064835337530403</v>
       </c>
       <c r="F8" s="21">
-        <v>0.0103715669875975</v>
+        <v>0.011514348009576578</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1964,19 +1964,19 @@
         <v>80</v>
       </c>
       <c r="B10" s="24">
-        <v>-0.7750763290749012</v>
+        <v>-0.7638663257182403</v>
       </c>
       <c r="C10" s="24">
-        <v>-0.4461108922229239</v>
+        <v>-0.43572630476102503</v>
       </c>
       <c r="D10" s="24">
-        <v>-0.2687570399259085</v>
+        <v>-0.2612171099500549</v>
       </c>
       <c r="E10" s="24">
-        <v>-0.16786741979741057</v>
+        <v>-0.1622994742641961</v>
       </c>
       <c r="F10" s="24">
-        <v>-0.1053452771446969</v>
+        <v>-0.10107118499026635</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1984,19 +1984,19 @@
         <v>81</v>
       </c>
       <c r="B11" s="21">
-        <v>-0.5472</v>
+        <v>-0.54</v>
       </c>
       <c r="C11" s="21">
-        <v>-0.35960000000000003</v>
+        <v>-0.35159999999999997</v>
       </c>
       <c r="D11" s="21">
-        <v>-0.2349</v>
+        <v>-0.2291</v>
       </c>
       <c r="E11" s="21">
-        <v>-0.1615</v>
+        <v>-0.1572</v>
       </c>
       <c r="F11" s="21">
-        <v>-0.1157</v>
+        <v>-0.11259999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2090,19 +2090,19 @@
         <v>18</v>
       </c>
       <c r="B6" s="18">
-        <v>42584380</v>
+        <v>42365105</v>
       </c>
       <c r="C6" s="18">
-        <v>44950179</v>
+        <v>44718722</v>
       </c>
       <c r="D6" s="18">
-        <v>47315978</v>
+        <v>47072339</v>
       </c>
       <c r="E6" s="18">
-        <v>49681777</v>
+        <v>49425956</v>
       </c>
       <c r="F6" s="18">
-        <v>52047576</v>
+        <v>51779573</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2110,19 +2110,19 @@
         <v>19</v>
       </c>
       <c r="B7" s="21">
-        <v>0.047615581112135485</v>
+        <v>0.047862031735788214</v>
       </c>
       <c r="C7" s="21">
-        <v>0.045109497784202375</v>
+        <v>0.045342977377573535</v>
       </c>
       <c r="D7" s="21">
-        <v>0.04285402279965554</v>
+        <v>0.043075828460531776</v>
       </c>
       <c r="E7" s="21">
-        <v>0.04081335496514144</v>
+        <v>0.04102459849233872</v>
       </c>
       <c r="F7" s="21">
-        <v>0.03895820239543913</v>
+        <v>0.039159843979400914</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2130,19 +2130,19 @@
         <v>90</v>
       </c>
       <c r="B8" s="16">
-        <v>27679847</v>
+        <v>27537318.25</v>
       </c>
       <c r="C8" s="16">
-        <v>29217616.35</v>
+        <v>29067169.3</v>
       </c>
       <c r="D8" s="16">
-        <v>30755385.7</v>
+        <v>30597020.35</v>
       </c>
       <c r="E8" s="16">
-        <v>32293155.05</v>
+        <v>32126871.400000002</v>
       </c>
       <c r="F8" s="16">
-        <v>33830924.4</v>
+        <v>33656722.45</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2150,19 +2150,19 @@
         <v>20</v>
       </c>
       <c r="B9" s="16">
-        <v>15181331.469999999</v>
+        <v>15103159.932499997</v>
       </c>
       <c r="C9" s="16">
-        <v>16024738.813500002</v>
+        <v>15942224.393000003</v>
       </c>
       <c r="D9" s="16">
-        <v>16868146.157</v>
+        <v>16781288.8535</v>
       </c>
       <c r="E9" s="16">
-        <v>17711553.500499997</v>
+        <v>17620353.314</v>
       </c>
       <c r="F9" s="16">
-        <v>18554960.844000004</v>
+        <v>18459417.774499997</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2170,19 +2170,19 @@
         <v>91</v>
       </c>
       <c r="B10" s="21">
-        <v>0.047615581112135485</v>
+        <v>0.047862031735788214</v>
       </c>
       <c r="C10" s="21">
-        <v>0.045109497784202375</v>
+        <v>0.045342977377573535</v>
       </c>
       <c r="D10" s="21">
-        <v>0.04285402279965554</v>
+        <v>0.043075828460531776</v>
       </c>
       <c r="E10" s="21">
-        <v>0.04081335496514144</v>
+        <v>0.04102459849233872</v>
       </c>
       <c r="F10" s="21">
-        <v>0.03895820239543913</v>
+        <v>0.039159843979400914</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2190,19 +2190,19 @@
         <v>92</v>
       </c>
       <c r="B11" s="21">
-        <v>0.04904404854549955</v>
+        <v>0.04929789268786186</v>
       </c>
       <c r="C11" s="21">
-        <v>0.04646278271772844</v>
+        <v>0.04670326669890074</v>
       </c>
       <c r="D11" s="21">
-        <v>0.044139643483645206</v>
+        <v>0.04436810331434773</v>
       </c>
       <c r="E11" s="21">
-        <v>0.04203775561409569</v>
+        <v>0.04225533644710888</v>
       </c>
       <c r="F11" s="21">
-        <v>0.0401269484673023</v>
+        <v>0.040334639298782934</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2210,19 +2210,19 @@
         <v>93</v>
       </c>
       <c r="B12" s="21">
-        <v>0.05051537000186454</v>
+        <v>0.05077682946849772</v>
       </c>
       <c r="C12" s="21">
-        <v>0.0478566661992603</v>
+        <v>0.04810436469986777</v>
       </c>
       <c r="D12" s="21">
-        <v>0.04546383278815457</v>
+        <v>0.04569914641377817</v>
       </c>
       <c r="E12" s="21">
-        <v>0.043298888282518565</v>
+        <v>0.043522996540522156</v>
       </c>
       <c r="F12" s="21">
-        <v>0.04133075692132138</v>
+        <v>0.041544678477746434</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -2230,19 +2230,19 @@
         <v>94</v>
       </c>
       <c r="B13" s="21">
-        <v>0.05203083110192047</v>
+        <v>0.05230013435255265</v>
       </c>
       <c r="C13" s="21">
-        <v>0.04929236618523811</v>
+        <v>0.0495474956408638</v>
       </c>
       <c r="D13" s="21">
-        <v>0.046827747771799204</v>
+        <v>0.04707012080619151</v>
       </c>
       <c r="E13" s="21">
-        <v>0.044597854930994114</v>
+        <v>0.04482868643673782</v>
       </c>
       <c r="F13" s="21">
-        <v>0.042570679628961015</v>
+        <v>0.04279101883207882</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -2250,19 +2250,19 @@
         <v>95</v>
       </c>
       <c r="B14" s="21">
-        <v>0.05359175603497809</v>
+        <v>0.053869138383129234</v>
       </c>
       <c r="C14" s="21">
-        <v>0.050771137170795254</v>
+        <v>0.05103392051008972</v>
       </c>
       <c r="D14" s="21">
-        <v>0.048232580204953183</v>
+        <v>0.04848222443037726</v>
       </c>
       <c r="E14" s="21">
-        <v>0.04593579057892394</v>
+        <v>0.04617354702983995</v>
       </c>
       <c r="F14" s="21">
-        <v>0.04384780001782985</v>
+        <v>0.04407474939704119</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -2270,19 +2270,19 @@
         <v>96</v>
       </c>
       <c r="B15" s="21">
-        <v>-0.014167117736270888</v>
+        <v>-0.01347581163906825</v>
       </c>
       <c r="C15" s="21">
-        <v>-0.021196804490641458</v>
+        <v>-0.020541882770105255</v>
       </c>
       <c r="D15" s="21">
-        <v>-0.02752352253986118</v>
+        <v>-0.026901346773027423</v>
       </c>
       <c r="E15" s="21">
-        <v>-0.03324769598870858</v>
+        <v>-0.03265514752532213</v>
       </c>
       <c r="F15" s="21">
-        <v>-0.038451490013119</v>
+        <v>-0.03788587547185174</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2290,19 +2290,19 @@
         <v>97</v>
       </c>
       <c r="B16" s="21">
-        <v>-0.010160196464562439</v>
+        <v>-0.00944815118444372</v>
       </c>
       <c r="C16" s="21">
-        <v>-0.017400773821564127</v>
+        <v>-0.016726204449411836</v>
       </c>
       <c r="D16" s="21">
-        <v>-0.02391729341226044</v>
+        <v>-0.02327645237242167</v>
       </c>
       <c r="E16" s="21">
-        <v>-0.029813192064573266</v>
+        <v>-0.029202867147285212</v>
       </c>
       <c r="F16" s="21">
-        <v>-0.03517309990971599</v>
+        <v>-0.03459051693221071</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -2310,19 +2310,19 @@
         <v>98</v>
       </c>
       <c r="B17" s="21">
-        <v>-0.006033067554702703</v>
+        <v>-0.005299660916180425</v>
       </c>
       <c r="C17" s="21">
-        <v>-0.013490862232414445</v>
+        <v>-0.012796055779097586</v>
       </c>
       <c r="D17" s="21">
-        <v>-0.020202877410831648</v>
+        <v>-0.019542811139797712</v>
       </c>
       <c r="E17" s="21">
-        <v>-0.026275653022713858</v>
+        <v>-0.025647018357907163</v>
       </c>
       <c r="F17" s="21">
-        <v>-0.03179635810321087</v>
+        <v>-0.03119629763638043</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -2330,19 +2330,19 @@
         <v>99</v>
       </c>
       <c r="B18" s="21">
-        <v>-0.001782124777547212</v>
+        <v>-0.0010267159398692658</v>
       </c>
       <c r="C18" s="21">
-        <v>-0.009463653295590306</v>
+        <v>-0.00874800264867394</v>
       </c>
       <c r="D18" s="21">
-        <v>-0.016377028929360025</v>
+        <v>-0.01569716067019507</v>
       </c>
       <c r="E18" s="21">
-        <v>-0.0226319878095987</v>
+        <v>-0.021984494104847804</v>
       </c>
       <c r="F18" s="21">
-        <v>-0.02831831404251062</v>
+        <v>-0.027700251761675267</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -2350,19 +2350,19 @@
         <v>100</v>
       </c>
       <c r="B19" s="21">
-        <v>0.0025963462829229613</v>
+        <v>0.0033744173857312453</v>
       </c>
       <c r="C19" s="21">
-        <v>-0.005315628090661427</v>
+        <v>-0.004578507924337571</v>
       </c>
       <c r="D19" s="21">
-        <v>-0.012436404993444236</v>
+        <v>-0.011736140686504335</v>
       </c>
       <c r="E19" s="21">
-        <v>-0.018879012640090072</v>
+        <v>-0.01821209412419665</v>
       </c>
       <c r="F19" s="21">
-        <v>-0.024735928659989352</v>
+        <v>-0.024099324510728937</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2370,19 +2370,19 @@
         <v>101</v>
       </c>
       <c r="B20" s="21">
-        <v>-0.1420896582266462</v>
+        <v>-0.13764925166607034</v>
       </c>
       <c r="C20" s="21">
-        <v>-0.18724283611856882</v>
+        <v>-0.18303613417200087</v>
       </c>
       <c r="D20" s="21">
-        <v>-0.22788069603033087</v>
+        <v>-0.22388432833139385</v>
       </c>
       <c r="E20" s="21">
-        <v>-0.2646482834135563</v>
+        <v>-0.2608422182064419</v>
       </c>
       <c r="F20" s="21">
-        <v>-0.29807336272467855</v>
+        <v>-0.29444029984564596</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -2390,19 +2390,19 @@
         <v>102</v>
       </c>
       <c r="B21" s="21">
-        <v>-0.03586139113652684</v>
+        <v>-0.033306241707776664</v>
       </c>
       <c r="C21" s="21">
-        <v>-0.06220988180163174</v>
+        <v>-0.05972620032456174</v>
       </c>
       <c r="D21" s="21">
-        <v>-0.08652544146342618</v>
+        <v>-0.08410763402950713</v>
       </c>
       <c r="E21" s="21">
-        <v>-0.10905601605248669</v>
+        <v>-0.10669917843247996</v>
       </c>
       <c r="F21" s="21">
-        <v>-0.13000924242274964</v>
+        <v>-0.12770904695409543</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -2410,19 +2410,19 @@
         <v>103</v>
       </c>
       <c r="B22" s="21">
-        <v>0.0023810908968516396</v>
+        <v>0.004194637147899107</v>
       </c>
       <c r="C22" s="21">
-        <v>-0.016402084788578443</v>
+        <v>-0.014625058162640085</v>
       </c>
       <c r="D22" s="21">
-        <v>-0.03387247517139475</v>
+        <v>-0.03212930021384783</v>
       </c>
       <c r="E22" s="21">
-        <v>-0.05018189282622802</v>
+        <v>-0.04847022066814334</v>
       </c>
       <c r="F22" s="21">
-        <v>-0.06545831602970974</v>
+        <v>-0.06377606539504015</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2430,19 +2430,19 @@
         <v>104</v>
       </c>
       <c r="B23" s="21">
-        <v>0.022049011024277275</v>
+        <v>0.02346888905624419</v>
       </c>
       <c r="C23" s="21">
-        <v>0.007314180847790248</v>
+        <v>0.008710490211712824</v>
       </c>
       <c r="D23" s="21">
-        <v>-0.00643928032601479</v>
+        <v>-0.0050648342056816755</v>
       </c>
       <c r="E23" s="21">
-        <v>-0.019322291176010968</v>
+        <v>-0.017968207916447942</v>
       </c>
       <c r="F23" s="21">
-        <v>-0.03142858986964064</v>
+        <v>-0.030093540747670462</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -2450,19 +2450,19 @@
         <v>105</v>
       </c>
       <c r="B24" s="21">
-        <v>0.03401699719623357</v>
+        <v>0.035193296433903065</v>
       </c>
       <c r="C24" s="21">
-        <v>0.02179768850191159</v>
+        <v>0.022956589424591077</v>
       </c>
       <c r="D24" s="21">
-        <v>0.010371567502016817</v>
+        <v>0.011514348950791215</v>
       </c>
       <c r="E24" s="21">
-        <v>-0.00035011756288312547</v>
+        <v>0.0007776666820694012</v>
       </c>
       <c r="F24" s="21">
-        <v>-0.010442435531213304</v>
+        <v>-0.009328656871202453</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2470,19 +2470,19 @@
         <v>106</v>
       </c>
       <c r="B25" s="21">
-        <v>-0.5344282516596186</v>
+        <v>-0.5219726932841608</v>
       </c>
       <c r="C25" s="21">
-        <v>-0.6610851321417172</v>
+        <v>-0.6492851266817792</v>
       </c>
       <c r="D25" s="21">
-        <v>-0.7750763240399099</v>
+        <v>-0.7638663164686537</v>
       </c>
       <c r="E25" s="21">
-        <v>-0.8782112115107918</v>
+        <v>-0.867535011769849</v>
       </c>
       <c r="F25" s="21">
-        <v>-0.9719701997607317</v>
+        <v>-0.9617792800431026</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2490,19 +2490,19 @@
         <v>107</v>
       </c>
       <c r="B26" s="21">
-        <v>-0.2521279658898481</v>
+        <v>-0.24333597682869468</v>
       </c>
       <c r="C26" s="21">
-        <v>-0.34760338718067885</v>
+        <v>-0.33817744635890856</v>
       </c>
       <c r="D26" s="21">
-        <v>-0.4461108875176999</v>
+        <v>-0.4357262962649081</v>
       </c>
       <c r="E26" s="21">
-        <v>-0.5517748028297751</v>
+        <v>-0.5398074249154957</v>
       </c>
       <c r="F26" s="21">
-        <v>-0.6733857171006318</v>
+        <v>-0.658261266549468</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -2510,19 +2510,19 @@
         <v>108</v>
       </c>
       <c r="B27" s="21">
-        <v>-0.12980392441659672</v>
+        <v>-0.1236178635097642</v>
       </c>
       <c r="C27" s="21">
-        <v>-0.19764252765342794</v>
+        <v>-0.19089318602223088</v>
       </c>
       <c r="D27" s="21">
-        <v>-0.26875703650847316</v>
+        <v>-0.2612171037847611</v>
       </c>
       <c r="E27" s="21">
-        <v>-0.3457393456187561</v>
+        <v>-0.3370181125665373</v>
       </c>
       <c r="F27" s="21">
-        <v>-0.43324900515272413</v>
+        <v>-0.4225649255719489</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -2530,19 +2530,19 @@
         <v>109</v>
       </c>
       <c r="B28" s="21">
-        <v>-0.06460965857350286</v>
+        <v>-0.059996211172250145</v>
       </c>
       <c r="C28" s="21">
-        <v>-0.11514981333440985</v>
+        <v>-0.1101285349593982</v>
       </c>
       <c r="D28" s="21">
-        <v>-0.16786741727453816</v>
+        <v>-0.16229946970863185</v>
       </c>
       <c r="E28" s="21">
-        <v>-0.224240613465051</v>
+        <v>-0.2179081766626951</v>
       </c>
       <c r="F28" s="21">
-        <v>-0.2866026937676257</v>
+        <v>-0.2791294417999801</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -2550,19 +2550,19 @@
         <v>110</v>
       </c>
       <c r="B29" s="21">
-        <v>-0.025258270635366686</v>
+        <v>-0.021648209823469815</v>
       </c>
       <c r="C29" s="21">
-        <v>-0.06465145530630582</v>
+        <v>-0.060752026027274086</v>
       </c>
       <c r="D29" s="21">
-        <v>-0.10534527520994878</v>
+        <v>-0.10107118149055902</v>
       </c>
       <c r="E29" s="21">
-        <v>-0.14821065748471898</v>
+        <v>-0.14343738838296272</v>
       </c>
       <c r="F29" s="21">
-        <v>-0.19448878986511953</v>
+        <v>-0.1890220999657974</v>
       </c>
     </row>
   </sheetData>
